--- a/Assets/ExcelDatas/MonsterData.xlsx
+++ b/Assets/ExcelDatas/MonsterData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project_Advence\Project_Advence\Assets\ExcelDatas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ProjectGit\Project_Advence_g\Assets\ExcelDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE07C649-69C5-4EF7-B114-5FA982AEFBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A782E7C6-6811-47EB-90D3-864EFFF90F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1704" windowWidth="16788" windowHeight="11256" firstSheet="1" activeTab="1" xr2:uid="{DFC90301-BE78-4300-908A-B9D6BBD09961}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11385" firstSheet="1" activeTab="1" xr2:uid="{DFC90301-BE78-4300-908A-B9D6BBD09961}"/>
   </bookViews>
   <sheets>
     <sheet name="Define" sheetId="4" state="hidden" r:id="rId1"/>
@@ -1068,9 +1068,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1108,7 +1108,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1214,7 +1214,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1356,7 +1356,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1365,15 +1365,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ED869AD-81BF-445A-BFB6-9DFC29F70ECE}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="13.2" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.59765625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.3984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.69921875" style="5"/>
+    <col min="2" max="2" width="14.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.75" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13.35" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="13.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>20</v>
       </c>
@@ -1384,7 +1384,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="13.35" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="13.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>21</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="13.35" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="13.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>24</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="13.35" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="13.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="11" t="s">
         <v>19</v>
@@ -1415,7 +1415,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="13.35" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="13.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="11" t="s">
         <v>16</v>
@@ -1436,21 +1436,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{255DB810-04DE-4682-BF12-874E2434A14F}">
   <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="11.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="14.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.09765625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.125" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1"/>
     <col min="9" max="10" width="9" style="1"/>
-    <col min="11" max="11" width="38.69921875" customWidth="1"/>
+    <col min="11" max="11" width="38.75" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="10.8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="11.25" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="10.8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" ht="11.25" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="10.8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" ht="11.25" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="10.8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" ht="11.25" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1010</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="10.8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" ht="11.25" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1011</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="10.8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" ht="11.25" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>1012</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="10.8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" ht="11.25" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>1013</v>
       </c>
@@ -1695,7 +1695,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="10.8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" ht="11.25" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1014</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="10.8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" ht="11.25" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>1015</v>
       </c>
@@ -1777,20 +1777,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36F41EFC-B4E4-4B06-882A-188E1EE7DA5E}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="10.8" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="19.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.625" style="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.59765625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.09765625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.19921875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="20" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.09765625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.125" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3000</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3001</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>3002</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>3003</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3004</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
